--- a/EX1/CPa vs. Baseline/CP vs baseline (precision recall)_test_set.xlsx
+++ b/EX1/CPa vs. Baseline/CP vs baseline (precision recall)_test_set.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\xhulj\Desktop\CPa\EX1\CPa vs. Baseline\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{438B6FAB-34D1-4640-A8D5-E9A7CD65EA63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8689D0A-F810-4D7A-93A1-D854DAE765C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21590" yWindow="5690" windowWidth="24910" windowHeight="14110" activeTab="2" xr2:uid="{73C30169-1CE3-4C80-BD02-1EEBAC63D7A2}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{73C30169-1CE3-4C80-BD02-1EEBAC63D7A2}"/>
   </bookViews>
   <sheets>
-    <sheet name="DeepJIT" sheetId="1" r:id="rId1"/>
-    <sheet name="CodeBERT4JIT" sheetId="2" r:id="rId2"/>
+    <sheet name="CodeBERT4JIT" sheetId="2" r:id="rId1"/>
+    <sheet name="DeepJIT" sheetId="1" r:id="rId2"/>
     <sheet name="LApredict" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -541,6 +541,962 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC062042-63AC-4BC2-888A-9BB2254AE71C}">
+  <dimension ref="A1:AJ13"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
+      <c r="H1" s="12"/>
+      <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="U1" s="12"/>
+      <c r="V1" s="12"/>
+      <c r="W1" s="12"/>
+      <c r="X1" s="12"/>
+      <c r="Y1" s="12"/>
+      <c r="Z1" s="12"/>
+      <c r="AA1" s="12"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+    </row>
+    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B2" s="12"/>
+      <c r="C2" s="1"/>
+      <c r="D2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="F2" s="1"/>
+      <c r="G2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="12"/>
+      <c r="I2" s="1"/>
+      <c r="J2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="1"/>
+      <c r="M2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="N2" s="13"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="3"/>
+      <c r="S2" s="1"/>
+      <c r="T2" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="U2" s="12"/>
+      <c r="V2" s="1"/>
+      <c r="W2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="X2" s="12"/>
+      <c r="Y2" s="1"/>
+      <c r="Z2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AA2" s="12"/>
+      <c r="AB2" s="1"/>
+      <c r="AC2" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="AD2" s="11"/>
+      <c r="AE2" s="1"/>
+      <c r="AF2" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="AG2" s="13"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="AJ2" s="13"/>
+    </row>
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="4"/>
+      <c r="D3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="H3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="L3" s="4"/>
+      <c r="M3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="O3" s="4"/>
+      <c r="P3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="R3" s="8"/>
+      <c r="S3" s="4"/>
+      <c r="T3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="U3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="V3" s="4"/>
+      <c r="W3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="X3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="Y3" s="4"/>
+      <c r="Z3" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="AA3" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="AB3" s="4"/>
+      <c r="AC3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AE3" s="4"/>
+      <c r="AF3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG3" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="AH3" s="4"/>
+      <c r="AI3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ3" s="7" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>0.893719806763285</v>
+      </c>
+      <c r="B4">
+        <v>0.92623814541622762</v>
+      </c>
+      <c r="D4">
+        <v>0.8867033831628639</v>
+      </c>
+      <c r="E4">
+        <v>0.88590604026845643</v>
+      </c>
+      <c r="G4">
+        <v>0.88111888111888115</v>
+      </c>
+      <c r="H4">
+        <v>0.84429327286470146</v>
+      </c>
+      <c r="J4">
+        <v>0.95854922279792742</v>
+      </c>
+      <c r="K4">
+        <v>0.76835664335664333</v>
+      </c>
+      <c r="M4">
+        <v>0.97322970639032813</v>
+      </c>
+      <c r="N4">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="P4">
+        <v>0.97927461139896377</v>
+      </c>
+      <c r="Q4">
+        <v>0.97639860139860135</v>
+      </c>
+      <c r="T4">
+        <v>0.93452134272689602</v>
+      </c>
+      <c r="U4">
+        <v>0.94799471132657553</v>
+      </c>
+      <c r="W4">
+        <v>0.93045953639690926</v>
+      </c>
+      <c r="X4">
+        <v>0.93071686023227873</v>
+      </c>
+      <c r="Z4">
+        <v>0.92865779927448611</v>
+      </c>
+      <c r="AA4">
+        <v>0.94543867306852902</v>
+      </c>
+      <c r="AC4">
+        <v>0.95550847457627119</v>
+      </c>
+      <c r="AD4">
+        <v>0.91337579617834397</v>
+      </c>
+      <c r="AF4">
+        <v>0.96949152542372885</v>
+      </c>
+      <c r="AG4">
+        <v>0.98683651804670913</v>
+      </c>
+      <c r="AI4">
+        <v>0.97627118644067801</v>
+      </c>
+      <c r="AJ4">
+        <v>0.91974522292993632</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>0.88490408673894916</v>
+      </c>
+      <c r="B5">
+        <v>0.92645654250238774</v>
+      </c>
+      <c r="D5">
+        <v>0.87964458804523427</v>
+      </c>
+      <c r="E5">
+        <v>0.88835341365461851</v>
+      </c>
+      <c r="G5">
+        <v>0.87450357426528991</v>
+      </c>
+      <c r="H5">
+        <v>0.87720644666155023</v>
+      </c>
+      <c r="J5">
+        <v>0.93151887620719931</v>
+      </c>
+      <c r="K5">
+        <v>0.84790209790209792</v>
+      </c>
+      <c r="M5">
+        <v>0.95610184372256368</v>
+      </c>
+      <c r="N5">
+        <v>0.96678321678321677</v>
+      </c>
+      <c r="P5">
+        <v>0.96663740122914843</v>
+      </c>
+      <c r="Q5">
+        <v>0.99912587412587417</v>
+      </c>
+      <c r="T5">
+        <v>0.93862212943632573</v>
+      </c>
+      <c r="U5">
+        <v>0.94191391558712911</v>
+      </c>
+      <c r="W5">
+        <v>0.93507554103715806</v>
+      </c>
+      <c r="X5">
+        <v>0.93266533066132262</v>
+      </c>
+      <c r="Z5">
+        <v>0.93223073820088742</v>
+      </c>
+      <c r="AA5">
+        <v>0.94797687861271673</v>
+      </c>
+      <c r="AC5">
+        <v>0.94692502106149956</v>
+      </c>
+      <c r="AD5">
+        <v>0.95711252653927814</v>
+      </c>
+      <c r="AF5">
+        <v>0.96461668070766637</v>
+      </c>
+      <c r="AG5">
+        <v>0.9881104033970276</v>
+      </c>
+      <c r="AI5">
+        <v>0.97346251053074984</v>
+      </c>
+      <c r="AJ5">
+        <v>0.90530785562632698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>0.89554794520547942</v>
+      </c>
+      <c r="B6">
+        <v>0.92216216216216218</v>
+      </c>
+      <c r="D6">
+        <v>0.88742810188989318</v>
+      </c>
+      <c r="E6">
+        <v>0.87572493786246897</v>
+      </c>
+      <c r="G6">
+        <v>0.88183279742765275</v>
+      </c>
+      <c r="H6">
+        <v>0.85648148148148151</v>
+      </c>
+      <c r="J6">
+        <v>0.91273996509598598</v>
+      </c>
+      <c r="K6">
+        <v>0.74562937062937062</v>
+      </c>
+      <c r="M6">
+        <v>0.94240837696335078</v>
+      </c>
+      <c r="N6">
+        <v>0.92395104895104896</v>
+      </c>
+      <c r="P6">
+        <v>0.95724258289703312</v>
+      </c>
+      <c r="Q6">
+        <v>0.97027972027972031</v>
+      </c>
+      <c r="T6">
+        <v>0.94592380172060631</v>
+      </c>
+      <c r="U6">
+        <v>0.94392917369308604</v>
+      </c>
+      <c r="W6">
+        <v>0.9399193548387097</v>
+      </c>
+      <c r="X6">
+        <v>0.92971246006389774</v>
+      </c>
+      <c r="Z6">
+        <v>0.93637454981992796</v>
+      </c>
+      <c r="AA6">
+        <v>0.95157068062827221</v>
+      </c>
+      <c r="AC6">
+        <v>0.97221052631578952</v>
+      </c>
+      <c r="AD6">
+        <v>0.95074309978768579</v>
+      </c>
+      <c r="AF6">
+        <v>0.98147368421052628</v>
+      </c>
+      <c r="AG6">
+        <v>0.98853503184713376</v>
+      </c>
+      <c r="AI6">
+        <v>0.98526315789473684</v>
+      </c>
+      <c r="AJ6">
+        <v>0.92611464968152868</v>
+      </c>
+    </row>
+    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>0.90533980582524276</v>
+      </c>
+      <c r="B7">
+        <v>0.93339960238568587</v>
+      </c>
+      <c r="D7">
+        <v>0.89655172413793105</v>
+      </c>
+      <c r="E7">
+        <v>0.90739236393176281</v>
+      </c>
+      <c r="G7">
+        <v>0.87004219409282701</v>
+      </c>
+      <c r="H7">
+        <v>0.88880368098159512</v>
+      </c>
+      <c r="J7">
+        <v>0.95396419437340152</v>
+      </c>
+      <c r="K7">
+        <v>0.82080419580419584</v>
+      </c>
+      <c r="M7">
+        <v>0.97527706734867858</v>
+      </c>
+      <c r="N7">
+        <v>0.97639860139860135</v>
+      </c>
+      <c r="P7">
+        <v>0.92715827338129497</v>
+      </c>
+      <c r="Q7">
+        <v>1.0131118881118881</v>
+      </c>
+      <c r="T7">
+        <v>0.93878389482333602</v>
+      </c>
+      <c r="U7">
+        <v>0.9583516001753617</v>
+      </c>
+      <c r="W7">
+        <v>0.93257973354864754</v>
+      </c>
+      <c r="X7">
+        <v>0.93637454981992796</v>
+      </c>
+      <c r="Z7">
+        <v>0.92951541850220265</v>
+      </c>
+      <c r="AA7">
+        <v>0.9569939183318853</v>
+      </c>
+      <c r="AC7">
+        <v>0.96617336152219868</v>
+      </c>
+      <c r="AD7">
+        <v>0.92823779193205946</v>
+      </c>
+      <c r="AF7">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="AG7">
+        <v>0.99363057324840764</v>
+      </c>
+      <c r="AI7">
+        <v>0.98139534883720925</v>
+      </c>
+      <c r="AJ7">
+        <v>0.93545647558386413</v>
+      </c>
+    </row>
+    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>0.90680713128038903</v>
+      </c>
+      <c r="B8">
+        <v>0.91902439024390248</v>
+      </c>
+      <c r="D8">
+        <v>0.90253565768621236</v>
+      </c>
+      <c r="E8">
+        <v>0.88169464428457234</v>
+      </c>
+      <c r="G8">
+        <v>0.89906103286384975</v>
+      </c>
+      <c r="H8">
+        <v>0.87490165224232885</v>
+      </c>
+      <c r="J8">
+        <v>0.95969125214408235</v>
+      </c>
+      <c r="K8">
+        <v>0.82342657342657344</v>
+      </c>
+      <c r="M8">
+        <v>0.97684391080617494</v>
+      </c>
+      <c r="N8">
+        <v>0.96416083916083917</v>
+      </c>
+      <c r="P8">
+        <v>0.98542024013722129</v>
+      </c>
+      <c r="Q8">
+        <v>0.97202797202797198</v>
+      </c>
+      <c r="T8">
+        <v>0.93430945785516417</v>
+      </c>
+      <c r="U8">
+        <v>0.95362449347140932</v>
+      </c>
+      <c r="W8">
+        <v>0.93309720582447853</v>
+      </c>
+      <c r="X8">
+        <v>0.9238020424194815</v>
+      </c>
+      <c r="Z8">
+        <v>0.93244304791830324</v>
+      </c>
+      <c r="AA8">
+        <v>0.93705710712796997</v>
+      </c>
+      <c r="AC8">
+        <v>0.9886934673366834</v>
+      </c>
+      <c r="AD8">
+        <v>0.89936305732484079</v>
+      </c>
+      <c r="AF8">
+        <v>0.99288107202680065</v>
+      </c>
+      <c r="AG8">
+        <v>0.99872611464968153</v>
+      </c>
+      <c r="AI8">
+        <v>0.9941373534338358</v>
+      </c>
+      <c r="AJ8">
+        <v>0.9545647558386412</v>
+      </c>
+    </row>
+    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="B9">
+        <v>0.94272076372315039</v>
+      </c>
+      <c r="D9">
+        <v>0.8775834658187599</v>
+      </c>
+      <c r="E9">
+        <v>0.90093936806148589</v>
+      </c>
+      <c r="G9">
+        <v>0.87705559906029762</v>
+      </c>
+      <c r="H9">
+        <v>0.8653122648607976</v>
+      </c>
+      <c r="J9">
+        <v>0.93755420641803988</v>
+      </c>
+      <c r="K9">
+        <v>0.69055944055944052</v>
+      </c>
+      <c r="M9">
+        <v>0.95750216825672163</v>
+      </c>
+      <c r="N9">
+        <v>0.92220279720279719</v>
+      </c>
+      <c r="P9">
+        <v>0.97137901127493498</v>
+      </c>
+      <c r="Q9">
+        <v>1.0052447552447552</v>
+      </c>
+      <c r="T9">
+        <v>0.93707954095765733</v>
+      </c>
+      <c r="U9">
+        <v>0.94927536231884058</v>
+      </c>
+      <c r="W9">
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="X9">
+        <v>0.9119718309859155</v>
+      </c>
+      <c r="Z9">
+        <v>0.93369948999607688</v>
+      </c>
+      <c r="AA9">
+        <v>0.94092465753424659</v>
+      </c>
+      <c r="AC9">
+        <v>0.98955286251567076</v>
+      </c>
+      <c r="AD9">
+        <v>0.89002123142250533</v>
+      </c>
+      <c r="AF9">
+        <v>0.99289594651065605</v>
+      </c>
+      <c r="AG9">
+        <v>0.98980891719745223</v>
+      </c>
+      <c r="AI9">
+        <v>0.9945674885081488</v>
+      </c>
+      <c r="AJ9">
+        <v>0.93333333333333335</v>
+      </c>
+    </row>
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>0.9087688219663419</v>
+      </c>
+      <c r="B10">
+        <v>0.95222584147665579</v>
+      </c>
+      <c r="D10">
+        <v>0.89342214820982513</v>
+      </c>
+      <c r="E10">
+        <v>0.90354492992580382</v>
+      </c>
+      <c r="G10">
+        <v>0.88952071486596263</v>
+      </c>
+      <c r="H10">
+        <v>0.88566953797963976</v>
+      </c>
+      <c r="J10">
+        <v>0.88831168831168827</v>
+      </c>
+      <c r="K10">
+        <v>0.76660839160839156</v>
+      </c>
+      <c r="M10">
+        <v>0.92900432900432905</v>
+      </c>
+      <c r="N10">
+        <v>0.95804195804195802</v>
+      </c>
+      <c r="P10">
+        <v>0.94805194805194803</v>
+      </c>
+      <c r="Q10">
+        <v>0.98863636363636365</v>
+      </c>
+      <c r="T10">
+        <v>0.9388254486133768</v>
+      </c>
+      <c r="U10">
+        <v>0.93644067796610164</v>
+      </c>
+      <c r="W10">
+        <v>0.93574297188755018</v>
+      </c>
+      <c r="X10">
+        <v>0.93038493038493042</v>
+      </c>
+      <c r="Z10">
+        <v>0.93349263241736358</v>
+      </c>
+      <c r="AA10">
+        <v>0.94757885384273655</v>
+      </c>
+      <c r="AC10">
+        <v>0.96885521885521886</v>
+      </c>
+      <c r="AD10">
+        <v>0.93842887473460723</v>
+      </c>
+      <c r="AF10">
+        <v>0.98063973063973064</v>
+      </c>
+      <c r="AG10">
+        <v>0.96475583864118897</v>
+      </c>
+      <c r="AI10">
+        <v>0.98653198653198648</v>
+      </c>
+      <c r="AJ10">
+        <v>0.90573248407643314</v>
+      </c>
+    </row>
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>0.90480349344978162</v>
+      </c>
+      <c r="B11">
+        <v>0.9211538461538461</v>
+      </c>
+      <c r="D11">
+        <v>0.88442622950819672</v>
+      </c>
+      <c r="E11">
+        <v>0.88452285485164395</v>
+      </c>
+      <c r="G11">
+        <v>0.88183279742765275</v>
+      </c>
+      <c r="H11">
+        <v>0.875</v>
+      </c>
+      <c r="J11">
+        <v>0.90559440559440563</v>
+      </c>
+      <c r="K11">
+        <v>0.83741258741258739</v>
+      </c>
+      <c r="M11">
+        <v>0.94318181818181823</v>
+      </c>
+      <c r="N11">
+        <v>0.96416083916083917</v>
+      </c>
+      <c r="P11">
+        <v>0.95891608391608396</v>
+      </c>
+      <c r="Q11">
+        <v>0.97290209790209792</v>
+      </c>
+      <c r="T11">
+        <v>0.94083574679354576</v>
+      </c>
+      <c r="U11">
+        <v>0.95440036479708157</v>
+      </c>
+      <c r="W11">
+        <v>0.93475634313330647</v>
+      </c>
+      <c r="X11">
+        <v>0.92961165048543692</v>
+      </c>
+      <c r="Z11">
+        <v>0.93062200956937802</v>
+      </c>
+      <c r="AA11">
+        <v>0.94659140251845419</v>
+      </c>
+      <c r="AC11">
+        <v>0.95707070707070707</v>
+      </c>
+      <c r="AD11">
+        <v>0.88874734607218686</v>
+      </c>
+      <c r="AF11">
+        <v>0.97685185185185186</v>
+      </c>
+      <c r="AG11">
+        <v>0.97579617834394905</v>
+      </c>
+      <c r="AI11">
+        <v>0.98232323232323238</v>
+      </c>
+      <c r="AJ11">
+        <v>0.92569002123142252</v>
+      </c>
+    </row>
+    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>0.89413988657844989</v>
+      </c>
+      <c r="B12">
+        <v>0.92144373673036095</v>
+      </c>
+      <c r="D12">
+        <v>0.87521815008726001</v>
+      </c>
+      <c r="E12">
+        <v>0.87915652879156525</v>
+      </c>
+      <c r="G12">
+        <v>0.8621553884711779</v>
+      </c>
+      <c r="H12">
+        <v>0.86833855799373039</v>
+      </c>
+      <c r="J12">
+        <v>0.85456187895212288</v>
+      </c>
+      <c r="K12">
+        <v>0.75874125874125875</v>
+      </c>
+      <c r="M12">
+        <v>0.90605239385727188</v>
+      </c>
+      <c r="N12">
+        <v>0.94755244755244761</v>
+      </c>
+      <c r="P12">
+        <v>0.9322493224932249</v>
+      </c>
+      <c r="Q12">
+        <v>0.96853146853146854</v>
+      </c>
+      <c r="T12">
+        <v>0.94558392632900801</v>
+      </c>
+      <c r="U12">
+        <v>0.94266055045871555</v>
+      </c>
+      <c r="W12">
+        <v>0.94175553732567674</v>
+      </c>
+      <c r="X12">
+        <v>0.90078740157480319</v>
+      </c>
+      <c r="Z12">
+        <v>0.93583535108958837</v>
+      </c>
+      <c r="AA12">
+        <v>0.9191542288557214</v>
+      </c>
+      <c r="AC12">
+        <v>0.95155855096882902</v>
+      </c>
+      <c r="AD12">
+        <v>0.87261146496815289</v>
+      </c>
+      <c r="AF12">
+        <v>0.96714406065711878</v>
+      </c>
+      <c r="AG12">
+        <v>0.97154989384288748</v>
+      </c>
+      <c r="AI12">
+        <v>0.97683235046335304</v>
+      </c>
+      <c r="AJ12">
+        <v>0.94140127388535033</v>
+      </c>
+    </row>
+    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>0.88264058679706603</v>
+      </c>
+      <c r="B13">
+        <v>0.93462717058222677</v>
+      </c>
+      <c r="D13">
+        <v>0.87440758293838861</v>
+      </c>
+      <c r="E13">
+        <v>0.88392156862745097</v>
+      </c>
+      <c r="G13">
+        <v>0.87215686274509807</v>
+      </c>
+      <c r="H13">
+        <v>0.84429327286470146</v>
+      </c>
+      <c r="J13">
+        <v>0.94502617801047117</v>
+      </c>
+      <c r="K13">
+        <v>0.79982517482517479</v>
+      </c>
+      <c r="M13">
+        <v>0.96596858638743455</v>
+      </c>
+      <c r="N13">
+        <v>0.9851398601398601</v>
+      </c>
+      <c r="P13">
+        <v>0.9703315881326352</v>
+      </c>
+      <c r="Q13">
+        <v>0.97639860139860135</v>
+      </c>
+      <c r="T13">
+        <v>0.93071786310517535</v>
+      </c>
+      <c r="U13">
+        <v>0.94927536231884058</v>
+      </c>
+      <c r="W13">
+        <v>0.92728758169934644</v>
+      </c>
+      <c r="X13">
+        <v>0.93637454981992796</v>
+      </c>
+      <c r="Z13">
+        <v>0.92494929006085191</v>
+      </c>
+      <c r="AA13">
+        <v>0.95157068062827221</v>
+      </c>
+      <c r="AC13">
+        <v>0.95380667236954664</v>
+      </c>
+      <c r="AD13">
+        <v>0.89002123142250533</v>
+      </c>
+      <c r="AF13">
+        <v>0.97091531223267746</v>
+      </c>
+      <c r="AG13">
+        <v>0.99363057324840764</v>
+      </c>
+      <c r="AI13">
+        <v>0.97519247219846017</v>
+      </c>
+      <c r="AJ13">
+        <v>0.92611464968152868</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="Z2:AA2"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AF2:AG2"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="T1:AA1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="P2:Q2"/>
+    <mergeCell ref="T2:U2"/>
+    <mergeCell ref="W2:X2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE2E1383-8622-41FE-BFB3-6AA0E2B6949C}">
   <dimension ref="A1:AJ14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -1500,8 +2456,8 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC062042-63AC-4BC2-888A-9BB2254AE71C}">
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD02547-4B56-4E32-8210-84D5892AAB0E}">
   <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
@@ -1697,962 +2653,6 @@
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.893719806763285</v>
-      </c>
-      <c r="B4">
-        <v>0.92623814541622762</v>
-      </c>
-      <c r="D4">
-        <v>0.8867033831628639</v>
-      </c>
-      <c r="E4">
-        <v>0.88590604026845643</v>
-      </c>
-      <c r="G4">
-        <v>0.88111888111888115</v>
-      </c>
-      <c r="H4">
-        <v>0.84429327286470146</v>
-      </c>
-      <c r="J4">
-        <v>0.95854922279792742</v>
-      </c>
-      <c r="K4">
-        <v>0.76835664335664333</v>
-      </c>
-      <c r="M4">
-        <v>0.97322970639032813</v>
-      </c>
-      <c r="N4">
-        <v>0.92307692307692313</v>
-      </c>
-      <c r="P4">
-        <v>0.97927461139896377</v>
-      </c>
-      <c r="Q4">
-        <v>0.97639860139860135</v>
-      </c>
-      <c r="T4">
-        <v>0.93452134272689602</v>
-      </c>
-      <c r="U4">
-        <v>0.94799471132657553</v>
-      </c>
-      <c r="W4">
-        <v>0.93045953639690926</v>
-      </c>
-      <c r="X4">
-        <v>0.93071686023227873</v>
-      </c>
-      <c r="Z4">
-        <v>0.92865779927448611</v>
-      </c>
-      <c r="AA4">
-        <v>0.94543867306852902</v>
-      </c>
-      <c r="AC4">
-        <v>0.95550847457627119</v>
-      </c>
-      <c r="AD4">
-        <v>0.91337579617834397</v>
-      </c>
-      <c r="AF4">
-        <v>0.96949152542372885</v>
-      </c>
-      <c r="AG4">
-        <v>0.98683651804670913</v>
-      </c>
-      <c r="AI4">
-        <v>0.97627118644067801</v>
-      </c>
-      <c r="AJ4">
-        <v>0.91974522292993632</v>
-      </c>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A5">
-        <v>0.88490408673894916</v>
-      </c>
-      <c r="B5">
-        <v>0.92645654250238774</v>
-      </c>
-      <c r="D5">
-        <v>0.87964458804523427</v>
-      </c>
-      <c r="E5">
-        <v>0.88835341365461851</v>
-      </c>
-      <c r="G5">
-        <v>0.87450357426528991</v>
-      </c>
-      <c r="H5">
-        <v>0.87720644666155023</v>
-      </c>
-      <c r="J5">
-        <v>0.93151887620719931</v>
-      </c>
-      <c r="K5">
-        <v>0.84790209790209792</v>
-      </c>
-      <c r="M5">
-        <v>0.95610184372256368</v>
-      </c>
-      <c r="N5">
-        <v>0.96678321678321677</v>
-      </c>
-      <c r="P5">
-        <v>0.96663740122914843</v>
-      </c>
-      <c r="Q5">
-        <v>0.99912587412587417</v>
-      </c>
-      <c r="T5">
-        <v>0.93862212943632573</v>
-      </c>
-      <c r="U5">
-        <v>0.94191391558712911</v>
-      </c>
-      <c r="W5">
-        <v>0.93507554103715806</v>
-      </c>
-      <c r="X5">
-        <v>0.93266533066132262</v>
-      </c>
-      <c r="Z5">
-        <v>0.93223073820088742</v>
-      </c>
-      <c r="AA5">
-        <v>0.94797687861271673</v>
-      </c>
-      <c r="AC5">
-        <v>0.94692502106149956</v>
-      </c>
-      <c r="AD5">
-        <v>0.95711252653927814</v>
-      </c>
-      <c r="AF5">
-        <v>0.96461668070766637</v>
-      </c>
-      <c r="AG5">
-        <v>0.9881104033970276</v>
-      </c>
-      <c r="AI5">
-        <v>0.97346251053074984</v>
-      </c>
-      <c r="AJ5">
-        <v>0.90530785562632698</v>
-      </c>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A6">
-        <v>0.89554794520547942</v>
-      </c>
-      <c r="B6">
-        <v>0.92216216216216218</v>
-      </c>
-      <c r="D6">
-        <v>0.88742810188989318</v>
-      </c>
-      <c r="E6">
-        <v>0.87572493786246897</v>
-      </c>
-      <c r="G6">
-        <v>0.88183279742765275</v>
-      </c>
-      <c r="H6">
-        <v>0.85648148148148151</v>
-      </c>
-      <c r="J6">
-        <v>0.91273996509598598</v>
-      </c>
-      <c r="K6">
-        <v>0.74562937062937062</v>
-      </c>
-      <c r="M6">
-        <v>0.94240837696335078</v>
-      </c>
-      <c r="N6">
-        <v>0.92395104895104896</v>
-      </c>
-      <c r="P6">
-        <v>0.95724258289703312</v>
-      </c>
-      <c r="Q6">
-        <v>0.97027972027972031</v>
-      </c>
-      <c r="T6">
-        <v>0.94592380172060631</v>
-      </c>
-      <c r="U6">
-        <v>0.94392917369308604</v>
-      </c>
-      <c r="W6">
-        <v>0.9399193548387097</v>
-      </c>
-      <c r="X6">
-        <v>0.92971246006389774</v>
-      </c>
-      <c r="Z6">
-        <v>0.93637454981992796</v>
-      </c>
-      <c r="AA6">
-        <v>0.95157068062827221</v>
-      </c>
-      <c r="AC6">
-        <v>0.97221052631578952</v>
-      </c>
-      <c r="AD6">
-        <v>0.95074309978768579</v>
-      </c>
-      <c r="AF6">
-        <v>0.98147368421052628</v>
-      </c>
-      <c r="AG6">
-        <v>0.98853503184713376</v>
-      </c>
-      <c r="AI6">
-        <v>0.98526315789473684</v>
-      </c>
-      <c r="AJ6">
-        <v>0.92611464968152868</v>
-      </c>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A7">
-        <v>0.90533980582524276</v>
-      </c>
-      <c r="B7">
-        <v>0.93339960238568587</v>
-      </c>
-      <c r="D7">
-        <v>0.89655172413793105</v>
-      </c>
-      <c r="E7">
-        <v>0.90739236393176281</v>
-      </c>
-      <c r="G7">
-        <v>0.87004219409282701</v>
-      </c>
-      <c r="H7">
-        <v>0.88880368098159512</v>
-      </c>
-      <c r="J7">
-        <v>0.95396419437340152</v>
-      </c>
-      <c r="K7">
-        <v>0.82080419580419584</v>
-      </c>
-      <c r="M7">
-        <v>0.97527706734867858</v>
-      </c>
-      <c r="N7">
-        <v>0.97639860139860135</v>
-      </c>
-      <c r="P7">
-        <v>0.92715827338129497</v>
-      </c>
-      <c r="Q7">
-        <v>1.0131118881118881</v>
-      </c>
-      <c r="T7">
-        <v>0.93878389482333602</v>
-      </c>
-      <c r="U7">
-        <v>0.9583516001753617</v>
-      </c>
-      <c r="W7">
-        <v>0.93257973354864754</v>
-      </c>
-      <c r="X7">
-        <v>0.93637454981992796</v>
-      </c>
-      <c r="Z7">
-        <v>0.92951541850220265</v>
-      </c>
-      <c r="AA7">
-        <v>0.9569939183318853</v>
-      </c>
-      <c r="AC7">
-        <v>0.96617336152219868</v>
-      </c>
-      <c r="AD7">
-        <v>0.92823779193205946</v>
-      </c>
-      <c r="AF7">
-        <v>0.97674418604651159</v>
-      </c>
-      <c r="AG7">
-        <v>0.99363057324840764</v>
-      </c>
-      <c r="AI7">
-        <v>0.98139534883720925</v>
-      </c>
-      <c r="AJ7">
-        <v>0.93545647558386413</v>
-      </c>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A8">
-        <v>0.90680713128038903</v>
-      </c>
-      <c r="B8">
-        <v>0.91902439024390248</v>
-      </c>
-      <c r="D8">
-        <v>0.90253565768621236</v>
-      </c>
-      <c r="E8">
-        <v>0.88169464428457234</v>
-      </c>
-      <c r="G8">
-        <v>0.89906103286384975</v>
-      </c>
-      <c r="H8">
-        <v>0.87490165224232885</v>
-      </c>
-      <c r="J8">
-        <v>0.95969125214408235</v>
-      </c>
-      <c r="K8">
-        <v>0.82342657342657344</v>
-      </c>
-      <c r="M8">
-        <v>0.97684391080617494</v>
-      </c>
-      <c r="N8">
-        <v>0.96416083916083917</v>
-      </c>
-      <c r="P8">
-        <v>0.98542024013722129</v>
-      </c>
-      <c r="Q8">
-        <v>0.97202797202797198</v>
-      </c>
-      <c r="T8">
-        <v>0.93430945785516417</v>
-      </c>
-      <c r="U8">
-        <v>0.95362449347140932</v>
-      </c>
-      <c r="W8">
-        <v>0.93309720582447853</v>
-      </c>
-      <c r="X8">
-        <v>0.9238020424194815</v>
-      </c>
-      <c r="Z8">
-        <v>0.93244304791830324</v>
-      </c>
-      <c r="AA8">
-        <v>0.93705710712796997</v>
-      </c>
-      <c r="AC8">
-        <v>0.9886934673366834</v>
-      </c>
-      <c r="AD8">
-        <v>0.89936305732484079</v>
-      </c>
-      <c r="AF8">
-        <v>0.99288107202680065</v>
-      </c>
-      <c r="AG8">
-        <v>0.99872611464968153</v>
-      </c>
-      <c r="AI8">
-        <v>0.9941373534338358</v>
-      </c>
-      <c r="AJ8">
-        <v>0.9545647558386412</v>
-      </c>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A9">
-        <v>0.88461538461538458</v>
-      </c>
-      <c r="B9">
-        <v>0.94272076372315039</v>
-      </c>
-      <c r="D9">
-        <v>0.8775834658187599</v>
-      </c>
-      <c r="E9">
-        <v>0.90093936806148589</v>
-      </c>
-      <c r="G9">
-        <v>0.87705559906029762</v>
-      </c>
-      <c r="H9">
-        <v>0.8653122648607976</v>
-      </c>
-      <c r="J9">
-        <v>0.93755420641803988</v>
-      </c>
-      <c r="K9">
-        <v>0.69055944055944052</v>
-      </c>
-      <c r="M9">
-        <v>0.95750216825672163</v>
-      </c>
-      <c r="N9">
-        <v>0.92220279720279719</v>
-      </c>
-      <c r="P9">
-        <v>0.97137901127493498</v>
-      </c>
-      <c r="Q9">
-        <v>1.0052447552447552</v>
-      </c>
-      <c r="T9">
-        <v>0.93707954095765733</v>
-      </c>
-      <c r="U9">
-        <v>0.94927536231884058</v>
-      </c>
-      <c r="W9">
-        <v>0.93617021276595747</v>
-      </c>
-      <c r="X9">
-        <v>0.9119718309859155</v>
-      </c>
-      <c r="Z9">
-        <v>0.93369948999607688</v>
-      </c>
-      <c r="AA9">
-        <v>0.94092465753424659</v>
-      </c>
-      <c r="AC9">
-        <v>0.98955286251567076</v>
-      </c>
-      <c r="AD9">
-        <v>0.89002123142250533</v>
-      </c>
-      <c r="AF9">
-        <v>0.99289594651065605</v>
-      </c>
-      <c r="AG9">
-        <v>0.98980891719745223</v>
-      </c>
-      <c r="AI9">
-        <v>0.9945674885081488</v>
-      </c>
-      <c r="AJ9">
-        <v>0.93333333333333335</v>
-      </c>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A10">
-        <v>0.9087688219663419</v>
-      </c>
-      <c r="B10">
-        <v>0.95222584147665579</v>
-      </c>
-      <c r="D10">
-        <v>0.89342214820982513</v>
-      </c>
-      <c r="E10">
-        <v>0.90354492992580382</v>
-      </c>
-      <c r="G10">
-        <v>0.88952071486596263</v>
-      </c>
-      <c r="H10">
-        <v>0.88566953797963976</v>
-      </c>
-      <c r="J10">
-        <v>0.88831168831168827</v>
-      </c>
-      <c r="K10">
-        <v>0.76660839160839156</v>
-      </c>
-      <c r="M10">
-        <v>0.92900432900432905</v>
-      </c>
-      <c r="N10">
-        <v>0.95804195804195802</v>
-      </c>
-      <c r="P10">
-        <v>0.94805194805194803</v>
-      </c>
-      <c r="Q10">
-        <v>0.98863636363636365</v>
-      </c>
-      <c r="T10">
-        <v>0.9388254486133768</v>
-      </c>
-      <c r="U10">
-        <v>0.93644067796610164</v>
-      </c>
-      <c r="W10">
-        <v>0.93574297188755018</v>
-      </c>
-      <c r="X10">
-        <v>0.93038493038493042</v>
-      </c>
-      <c r="Z10">
-        <v>0.93349263241736358</v>
-      </c>
-      <c r="AA10">
-        <v>0.94757885384273655</v>
-      </c>
-      <c r="AC10">
-        <v>0.96885521885521886</v>
-      </c>
-      <c r="AD10">
-        <v>0.93842887473460723</v>
-      </c>
-      <c r="AF10">
-        <v>0.98063973063973064</v>
-      </c>
-      <c r="AG10">
-        <v>0.96475583864118897</v>
-      </c>
-      <c r="AI10">
-        <v>0.98653198653198648</v>
-      </c>
-      <c r="AJ10">
-        <v>0.90573248407643314</v>
-      </c>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A11">
-        <v>0.90480349344978162</v>
-      </c>
-      <c r="B11">
-        <v>0.9211538461538461</v>
-      </c>
-      <c r="D11">
-        <v>0.88442622950819672</v>
-      </c>
-      <c r="E11">
-        <v>0.88452285485164395</v>
-      </c>
-      <c r="G11">
-        <v>0.88183279742765275</v>
-      </c>
-      <c r="H11">
-        <v>0.875</v>
-      </c>
-      <c r="J11">
-        <v>0.90559440559440563</v>
-      </c>
-      <c r="K11">
-        <v>0.83741258741258739</v>
-      </c>
-      <c r="M11">
-        <v>0.94318181818181823</v>
-      </c>
-      <c r="N11">
-        <v>0.96416083916083917</v>
-      </c>
-      <c r="P11">
-        <v>0.95891608391608396</v>
-      </c>
-      <c r="Q11">
-        <v>0.97290209790209792</v>
-      </c>
-      <c r="T11">
-        <v>0.94083574679354576</v>
-      </c>
-      <c r="U11">
-        <v>0.95440036479708157</v>
-      </c>
-      <c r="W11">
-        <v>0.93475634313330647</v>
-      </c>
-      <c r="X11">
-        <v>0.92961165048543692</v>
-      </c>
-      <c r="Z11">
-        <v>0.93062200956937802</v>
-      </c>
-      <c r="AA11">
-        <v>0.94659140251845419</v>
-      </c>
-      <c r="AC11">
-        <v>0.95707070707070707</v>
-      </c>
-      <c r="AD11">
-        <v>0.88874734607218686</v>
-      </c>
-      <c r="AF11">
-        <v>0.97685185185185186</v>
-      </c>
-      <c r="AG11">
-        <v>0.97579617834394905</v>
-      </c>
-      <c r="AI11">
-        <v>0.98232323232323238</v>
-      </c>
-      <c r="AJ11">
-        <v>0.92569002123142252</v>
-      </c>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A12">
-        <v>0.89413988657844989</v>
-      </c>
-      <c r="B12">
-        <v>0.92144373673036095</v>
-      </c>
-      <c r="D12">
-        <v>0.87521815008726001</v>
-      </c>
-      <c r="E12">
-        <v>0.87915652879156525</v>
-      </c>
-      <c r="G12">
-        <v>0.8621553884711779</v>
-      </c>
-      <c r="H12">
-        <v>0.86833855799373039</v>
-      </c>
-      <c r="J12">
-        <v>0.85456187895212288</v>
-      </c>
-      <c r="K12">
-        <v>0.75874125874125875</v>
-      </c>
-      <c r="M12">
-        <v>0.90605239385727188</v>
-      </c>
-      <c r="N12">
-        <v>0.94755244755244761</v>
-      </c>
-      <c r="P12">
-        <v>0.9322493224932249</v>
-      </c>
-      <c r="Q12">
-        <v>0.96853146853146854</v>
-      </c>
-      <c r="T12">
-        <v>0.94558392632900801</v>
-      </c>
-      <c r="U12">
-        <v>0.94266055045871555</v>
-      </c>
-      <c r="W12">
-        <v>0.94175553732567674</v>
-      </c>
-      <c r="X12">
-        <v>0.90078740157480319</v>
-      </c>
-      <c r="Z12">
-        <v>0.93583535108958837</v>
-      </c>
-      <c r="AA12">
-        <v>0.9191542288557214</v>
-      </c>
-      <c r="AC12">
-        <v>0.95155855096882902</v>
-      </c>
-      <c r="AD12">
-        <v>0.87261146496815289</v>
-      </c>
-      <c r="AF12">
-        <v>0.96714406065711878</v>
-      </c>
-      <c r="AG12">
-        <v>0.97154989384288748</v>
-      </c>
-      <c r="AI12">
-        <v>0.97683235046335304</v>
-      </c>
-      <c r="AJ12">
-        <v>0.94140127388535033</v>
-      </c>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A13">
-        <v>0.88264058679706603</v>
-      </c>
-      <c r="B13">
-        <v>0.93462717058222677</v>
-      </c>
-      <c r="D13">
-        <v>0.87440758293838861</v>
-      </c>
-      <c r="E13">
-        <v>0.88392156862745097</v>
-      </c>
-      <c r="G13">
-        <v>0.87215686274509807</v>
-      </c>
-      <c r="H13">
-        <v>0.84429327286470146</v>
-      </c>
-      <c r="J13">
-        <v>0.94502617801047117</v>
-      </c>
-      <c r="K13">
-        <v>0.79982517482517479</v>
-      </c>
-      <c r="M13">
-        <v>0.96596858638743455</v>
-      </c>
-      <c r="N13">
-        <v>0.9851398601398601</v>
-      </c>
-      <c r="P13">
-        <v>0.9703315881326352</v>
-      </c>
-      <c r="Q13">
-        <v>0.97639860139860135</v>
-      </c>
-      <c r="T13">
-        <v>0.93071786310517535</v>
-      </c>
-      <c r="U13">
-        <v>0.94927536231884058</v>
-      </c>
-      <c r="W13">
-        <v>0.92728758169934644</v>
-      </c>
-      <c r="X13">
-        <v>0.93637454981992796</v>
-      </c>
-      <c r="Z13">
-        <v>0.92494929006085191</v>
-      </c>
-      <c r="AA13">
-        <v>0.95157068062827221</v>
-      </c>
-      <c r="AC13">
-        <v>0.95380667236954664</v>
-      </c>
-      <c r="AD13">
-        <v>0.89002123142250533</v>
-      </c>
-      <c r="AF13">
-        <v>0.97091531223267746</v>
-      </c>
-      <c r="AG13">
-        <v>0.99363057324840764</v>
-      </c>
-      <c r="AI13">
-        <v>0.97519247219846017</v>
-      </c>
-      <c r="AJ13">
-        <v>0.92611464968152868</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="14">
-    <mergeCell ref="Z2:AA2"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AF2:AG2"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="T1:AA1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="J2:K2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="P2:Q2"/>
-    <mergeCell ref="T2:U2"/>
-    <mergeCell ref="W2:X2"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1BD02547-4B56-4E32-8210-84D5892AAB0E}">
-  <dimension ref="A1:AJ13"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A1" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-      <c r="G1" s="12"/>
-      <c r="H1" s="12"/>
-      <c r="I1" s="1"/>
-      <c r="J1" s="1"/>
-      <c r="K1" s="1"/>
-      <c r="L1" s="1"/>
-      <c r="M1" s="1"/>
-      <c r="N1" s="1"/>
-      <c r="O1" s="1"/>
-      <c r="P1" s="1"/>
-      <c r="Q1" s="1"/>
-      <c r="R1" s="1"/>
-      <c r="S1" s="1"/>
-      <c r="T1" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="U1" s="12"/>
-      <c r="V1" s="12"/>
-      <c r="W1" s="12"/>
-      <c r="X1" s="12"/>
-      <c r="Y1" s="12"/>
-      <c r="Z1" s="12"/>
-      <c r="AA1" s="12"/>
-      <c r="AB1" s="1"/>
-      <c r="AC1" s="1"/>
-      <c r="AD1" s="1"/>
-      <c r="AE1" s="1"/>
-      <c r="AF1" s="1"/>
-      <c r="AG1" s="1"/>
-      <c r="AH1" s="1"/>
-      <c r="AI1" s="1"/>
-      <c r="AJ1" s="1"/>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="12"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="12"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="11"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="N2" s="13"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="Q2" s="13"/>
-      <c r="R2" s="3"/>
-      <c r="S2" s="1"/>
-      <c r="T2" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="U2" s="12"/>
-      <c r="V2" s="1"/>
-      <c r="W2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="X2" s="12"/>
-      <c r="Y2" s="1"/>
-      <c r="Z2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="AA2" s="12"/>
-      <c r="AB2" s="1"/>
-      <c r="AC2" s="10" t="s">
-        <v>2</v>
-      </c>
-      <c r="AD2" s="11"/>
-      <c r="AE2" s="1"/>
-      <c r="AF2" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="AG2" s="13"/>
-      <c r="AH2" s="2"/>
-      <c r="AI2" s="12" t="s">
-        <v>4</v>
-      </c>
-      <c r="AJ2" s="13"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="4"/>
-      <c r="D3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="K3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="L3" s="4"/>
-      <c r="M3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="O3" s="4"/>
-      <c r="P3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="R3" s="8"/>
-      <c r="S3" s="4"/>
-      <c r="T3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="U3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="V3" s="4"/>
-      <c r="W3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="X3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="Y3" s="4"/>
-      <c r="Z3" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="AA3" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="AB3" s="4"/>
-      <c r="AC3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AD3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AE3" s="4"/>
-      <c r="AF3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="AH3" s="4"/>
-      <c r="AI3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="AJ3" s="7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A4">
         <v>0.94594594594594594</v>
       </c>
       <c r="B4">
